--- a/output/第10期計画_調査結果と年報実績の突合クロス集計.xlsx
+++ b/output/第10期計画_調査結果と年報実績の突合クロス集計.xlsx
@@ -912,7 +912,7 @@
       <c r="D7" s="6" t="inlineStr">
         <is>
           <t>計画素案 第6章第4節4
-サービス見込量 第1次概算</t>
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
